--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -733,7 +733,7 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="1">
-    <x:tablePart r:id="rId1"/>
+    <x:tablePart r:id="rId10"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -76,7 +76,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -86,6 +86,13 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -580,6 +580,8 @@
       <x:c r="C3" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="D3" s="0" t="s"/>
+      <x:c r="E3" s="0" t="s"/>
       <x:c r="F3" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -598,6 +600,8 @@
       <x:c r="C4" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D4" s="0" t="s"/>
+      <x:c r="E4" s="0" t="s"/>
       <x:c r="F4" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -616,6 +620,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s"/>
+      <x:c r="D5" s="0" t="s"/>
+      <x:c r="E5" s="0" t="s"/>
       <x:c r="F5" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -636,6 +642,8 @@
       <x:c r="C6" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D6" s="0" t="s"/>
+      <x:c r="E6" s="0" t="s"/>
       <x:c r="F6" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -656,6 +664,8 @@
       <x:c r="C7" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="D7" s="0" t="s"/>
+      <x:c r="E7" s="0" t="s"/>
       <x:c r="F7" s="8" t="s"/>
       <x:c r="G7" s="8" t="s">
         <x:v>7</x:v>
@@ -672,6 +682,8 @@
       <x:c r="C8" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D8" s="0" t="s"/>
+      <x:c r="E8" s="0" t="s"/>
       <x:c r="F8" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -690,6 +702,8 @@
       <x:c r="C9" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="D9" s="0" t="s"/>
+      <x:c r="E9" s="0" t="s"/>
       <x:c r="F9" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -708,6 +722,8 @@
       <x:c r="C10" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D10" s="0" t="s"/>
+      <x:c r="E10" s="0" t="s"/>
       <x:c r="F10" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -970,6 +986,8 @@
       <x:c r="C5" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D5" s="0" t="s"/>
+      <x:c r="E5" s="0" t="s"/>
       <x:c r="F5" s="8" t="s"/>
       <x:c r="G5" s="8" t="s">
         <x:v>7</x:v>
@@ -986,6 +1004,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s"/>
+      <x:c r="D6" s="0" t="s"/>
+      <x:c r="E6" s="0" t="s"/>
       <x:c r="F6" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1006,6 +1026,8 @@
       <x:c r="C7" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D7" s="0" t="s"/>
+      <x:c r="E7" s="0" t="s"/>
       <x:c r="F7" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1026,6 +1048,8 @@
       <x:c r="C8" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="D8" s="0" t="s"/>
+      <x:c r="E8" s="0" t="s"/>
       <x:c r="F8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1044,6 +1068,8 @@
       <x:c r="C9" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D9" s="0" t="s"/>
+      <x:c r="E9" s="0" t="s"/>
       <x:c r="F9" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1064,6 +1090,8 @@
       <x:c r="C10" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="D10" s="0" t="s"/>
+      <x:c r="E10" s="0" t="s"/>
       <x:c r="F10" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1082,6 +1110,8 @@
       <x:c r="C11" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D11" s="0" t="s"/>
+      <x:c r="E11" s="0" t="s"/>
       <x:c r="F11" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1098,6 +1128,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s"/>
+      <x:c r="D12" s="0" t="s"/>
+      <x:c r="E12" s="0" t="s"/>
       <x:c r="F12" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1143,6 +1175,8 @@
       <x:c r="C3" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D3" s="0" t="s"/>
+      <x:c r="E3" s="0" t="s"/>
       <x:c r="F3" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1159,6 +1193,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s"/>
+      <x:c r="D4" s="0" t="s"/>
+      <x:c r="E4" s="0" t="s"/>
       <x:c r="F4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1177,6 +1213,8 @@
       <x:c r="C5" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D5" s="0" t="s"/>
+      <x:c r="E5" s="0" t="s"/>
       <x:c r="F5" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1197,6 +1235,8 @@
       <x:c r="C6" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="D6" s="0" t="s"/>
+      <x:c r="E6" s="0" t="s"/>
       <x:c r="F6" s="8" t="s"/>
       <x:c r="G6" s="8" t="s">
         <x:v>7</x:v>
@@ -1213,6 +1253,8 @@
       <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D7" s="0" t="s"/>
+      <x:c r="E7" s="0" t="s"/>
       <x:c r="F7" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1233,6 +1275,8 @@
       <x:c r="C8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="D8" s="0" t="s"/>
+      <x:c r="E8" s="0" t="s"/>
       <x:c r="F8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1253,6 +1297,8 @@
       <x:c r="C9" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D9" s="0" t="s"/>
+      <x:c r="E9" s="0" t="s"/>
       <x:c r="F9" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1271,6 +1317,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="9" t="s"/>
+      <x:c r="D10" s="0" t="s"/>
+      <x:c r="E10" s="0" t="s"/>
       <x:c r="F10" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1312,6 +1360,8 @@
       <x:c r="A3" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="B3" s="0" t="s"/>
+      <x:c r="C3" s="0" t="s"/>
       <x:c r="D3" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1320,6 +1370,8 @@
       <x:c r="A4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="B4" s="0" t="s"/>
+      <x:c r="C4" s="0" t="s"/>
       <x:c r="D4" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1328,18 +1380,24 @@
       <x:c r="A5" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="B5" s="0" t="s"/>
+      <x:c r="C5" s="0" t="s"/>
       <x:c r="D5" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="5" t="s"/>
+      <x:c r="B6" s="0" t="s"/>
+      <x:c r="C6" s="0" t="s"/>
       <x:c r="D6" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="8" t="s"/>
+      <x:c r="B7" s="0" t="s"/>
+      <x:c r="C7" s="0" t="s"/>
       <x:c r="D7" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1348,6 +1406,8 @@
       <x:c r="A8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="B8" s="0" t="s"/>
+      <x:c r="C8" s="0" t="s"/>
       <x:c r="D8" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1356,12 +1416,16 @@
       <x:c r="A9" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="B9" s="0" t="s"/>
+      <x:c r="C9" s="0" t="s"/>
       <x:c r="D9" s="8" t="s"/>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
+      <x:c r="B10" s="0" t="s"/>
+      <x:c r="C10" s="0" t="s"/>
       <x:c r="D10" s="5" t="s"/>
     </x:row>
   </x:sheetData>
@@ -1401,6 +1465,8 @@
       <x:c r="C3" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D3" s="0" t="s"/>
+      <x:c r="E3" s="0" t="s"/>
       <x:c r="F3" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1419,6 +1485,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s"/>
+      <x:c r="D4" s="0" t="s"/>
+      <x:c r="E4" s="0" t="s"/>
       <x:c r="F4" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1439,6 +1507,8 @@
       <x:c r="C5" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D5" s="0" t="s"/>
+      <x:c r="E5" s="0" t="s"/>
       <x:c r="F5" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1459,6 +1529,8 @@
       <x:c r="C6" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="D6" s="0" t="s"/>
+      <x:c r="E6" s="0" t="s"/>
       <x:c r="F6" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1475,6 +1547,8 @@
       <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D7" s="0" t="s"/>
+      <x:c r="E7" s="0" t="s"/>
       <x:c r="F7" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1495,6 +1569,8 @@
       <x:c r="C8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="D8" s="0" t="s"/>
+      <x:c r="E8" s="0" t="s"/>
       <x:c r="F8" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1513,6 +1589,8 @@
       <x:c r="C9" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D9" s="0" t="s"/>
+      <x:c r="E9" s="0" t="s"/>
       <x:c r="F9" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1529,6 +1607,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="9" t="s"/>
+      <x:c r="D10" s="0" t="s"/>
+      <x:c r="E10" s="0" t="s"/>
       <x:c r="F10" s="8" t="s"/>
       <x:c r="G10" s="8" t="s">
         <x:v>7</x:v>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -580,8 +580,6 @@
       <x:c r="C3" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s"/>
-      <x:c r="E3" s="0" t="s"/>
       <x:c r="F3" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -600,8 +598,6 @@
       <x:c r="C4" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s"/>
-      <x:c r="E4" s="0" t="s"/>
       <x:c r="F4" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -620,8 +616,6 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s"/>
-      <x:c r="D5" s="0" t="s"/>
-      <x:c r="E5" s="0" t="s"/>
       <x:c r="F5" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -642,8 +636,6 @@
       <x:c r="C6" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s"/>
-      <x:c r="E6" s="0" t="s"/>
       <x:c r="F6" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -664,8 +656,6 @@
       <x:c r="C7" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s"/>
-      <x:c r="E7" s="0" t="s"/>
       <x:c r="F7" s="8" t="s"/>
       <x:c r="G7" s="8" t="s">
         <x:v>7</x:v>
@@ -682,8 +672,6 @@
       <x:c r="C8" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s"/>
-      <x:c r="E8" s="0" t="s"/>
       <x:c r="F8" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -702,8 +690,6 @@
       <x:c r="C9" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s"/>
-      <x:c r="E9" s="0" t="s"/>
       <x:c r="F9" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -722,8 +708,6 @@
       <x:c r="C10" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D10" s="0" t="s"/>
-      <x:c r="E10" s="0" t="s"/>
       <x:c r="F10" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -986,8 +970,6 @@
       <x:c r="C5" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s"/>
-      <x:c r="E5" s="0" t="s"/>
       <x:c r="F5" s="8" t="s"/>
       <x:c r="G5" s="8" t="s">
         <x:v>7</x:v>
@@ -1004,8 +986,6 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s"/>
-      <x:c r="D6" s="0" t="s"/>
-      <x:c r="E6" s="0" t="s"/>
       <x:c r="F6" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1026,8 +1006,6 @@
       <x:c r="C7" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s"/>
-      <x:c r="E7" s="0" t="s"/>
       <x:c r="F7" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1048,8 +1026,6 @@
       <x:c r="C8" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s"/>
-      <x:c r="E8" s="0" t="s"/>
       <x:c r="F8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1068,8 +1044,6 @@
       <x:c r="C9" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s"/>
-      <x:c r="E9" s="0" t="s"/>
       <x:c r="F9" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1090,8 +1064,6 @@
       <x:c r="C10" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D10" s="0" t="s"/>
-      <x:c r="E10" s="0" t="s"/>
       <x:c r="F10" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1110,8 +1082,6 @@
       <x:c r="C11" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D11" s="0" t="s"/>
-      <x:c r="E11" s="0" t="s"/>
       <x:c r="F11" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1128,8 +1098,6 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s"/>
-      <x:c r="D12" s="0" t="s"/>
-      <x:c r="E12" s="0" t="s"/>
       <x:c r="F12" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1175,8 +1143,6 @@
       <x:c r="C3" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s"/>
-      <x:c r="E3" s="0" t="s"/>
       <x:c r="F3" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1193,8 +1159,6 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s"/>
-      <x:c r="D4" s="0" t="s"/>
-      <x:c r="E4" s="0" t="s"/>
       <x:c r="F4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1213,8 +1177,6 @@
       <x:c r="C5" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s"/>
-      <x:c r="E5" s="0" t="s"/>
       <x:c r="F5" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1235,8 +1197,6 @@
       <x:c r="C6" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s"/>
-      <x:c r="E6" s="0" t="s"/>
       <x:c r="F6" s="8" t="s"/>
       <x:c r="G6" s="8" t="s">
         <x:v>7</x:v>
@@ -1253,8 +1213,6 @@
       <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s"/>
-      <x:c r="E7" s="0" t="s"/>
       <x:c r="F7" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1275,8 +1233,6 @@
       <x:c r="C8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s"/>
-      <x:c r="E8" s="0" t="s"/>
       <x:c r="F8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1297,8 +1253,6 @@
       <x:c r="C9" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s"/>
-      <x:c r="E9" s="0" t="s"/>
       <x:c r="F9" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1317,8 +1271,6 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="9" t="s"/>
-      <x:c r="D10" s="0" t="s"/>
-      <x:c r="E10" s="0" t="s"/>
       <x:c r="F10" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1360,8 +1312,6 @@
       <x:c r="A3" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s"/>
-      <x:c r="C3" s="0" t="s"/>
       <x:c r="D3" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1370,8 +1320,6 @@
       <x:c r="A4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s"/>
-      <x:c r="C4" s="0" t="s"/>
       <x:c r="D4" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1380,24 +1328,18 @@
       <x:c r="A5" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s"/>
-      <x:c r="C5" s="0" t="s"/>
       <x:c r="D5" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="5" t="s"/>
-      <x:c r="B6" s="0" t="s"/>
-      <x:c r="C6" s="0" t="s"/>
       <x:c r="D6" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="8" t="s"/>
-      <x:c r="B7" s="0" t="s"/>
-      <x:c r="C7" s="0" t="s"/>
       <x:c r="D7" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1406,8 +1348,6 @@
       <x:c r="A8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s"/>
-      <x:c r="C8" s="0" t="s"/>
       <x:c r="D8" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1416,16 +1356,12 @@
       <x:c r="A9" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s"/>
-      <x:c r="C9" s="0" t="s"/>
       <x:c r="D9" s="8" t="s"/>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s"/>
-      <x:c r="C10" s="0" t="s"/>
       <x:c r="D10" s="5" t="s"/>
     </x:row>
   </x:sheetData>
@@ -1465,8 +1401,6 @@
       <x:c r="C3" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s"/>
-      <x:c r="E3" s="0" t="s"/>
       <x:c r="F3" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1485,8 +1419,6 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s"/>
-      <x:c r="D4" s="0" t="s"/>
-      <x:c r="E4" s="0" t="s"/>
       <x:c r="F4" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1507,8 +1439,6 @@
       <x:c r="C5" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s"/>
-      <x:c r="E5" s="0" t="s"/>
       <x:c r="F5" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1529,8 +1459,6 @@
       <x:c r="C6" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s"/>
-      <x:c r="E6" s="0" t="s"/>
       <x:c r="F6" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1547,8 +1475,6 @@
       <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s"/>
-      <x:c r="E7" s="0" t="s"/>
       <x:c r="F7" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1569,8 +1495,6 @@
       <x:c r="C8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s"/>
-      <x:c r="E8" s="0" t="s"/>
       <x:c r="F8" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1589,8 +1513,6 @@
       <x:c r="C9" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s"/>
-      <x:c r="E9" s="0" t="s"/>
       <x:c r="F9" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1607,8 +1529,6 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="9" t="s"/>
-      <x:c r="D10" s="0" t="s"/>
-      <x:c r="E10" s="0" t="s"/>
       <x:c r="F10" s="8" t="s"/>
       <x:c r="G10" s="8" t="s">
         <x:v>7</x:v>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -109,14 +109,20 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1E90FF"/>
+        <x:bgColor rgb="FF1E90FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
         <x:bgColor rgb="FF90EE90"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1E90FF"/>
-        <x:bgColor rgb="FF1E90FF"/>
+        <x:fgColor rgb="FFA9A9A9"/>
+        <x:bgColor rgb="FFA9A9A9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -127,20 +133,14 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA9A9A9"/>
-        <x:bgColor rgb="FFA9A9A9"/>
+        <x:fgColor rgb="FFCD5C5C"/>
+        <x:bgColor rgb="FFCD5C5C"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDEB887"/>
         <x:bgColor rgb="FFDEB887"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFCD5C5C"/>
-        <x:bgColor rgb="FFCD5C5C"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -591,69 +591,69 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H4" s="3" t="s">
+      <x:c r="A4" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H4" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s"/>
-      <x:c r="F5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H5" s="5" t="s">
+      <x:c r="A5" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s"/>
+      <x:c r="F5" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H5" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G6" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="7" t="s">
+      <x:c r="A6" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
+      <x:c r="A7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="F7" s="8" t="s"/>
@@ -672,22 +672,22 @@
       <x:c r="C8" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F8" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H8" s="4" t="s"/>
+      <x:c r="F8" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="s"/>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="3" t="s">
+      <x:c r="A9" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="s">
@@ -699,22 +699,22 @@
       <x:c r="H9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F10" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H10" s="6" t="s">
+      <x:c r="A10" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F10" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G10" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -726,11 +726,11 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="9" t="s"/>
-      <x:c r="F11" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G11" s="2" t="s"/>
-      <x:c r="H11" s="2" t="s">
+      <x:c r="F11" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="s"/>
+      <x:c r="H11" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -760,23 +760,23 @@
     </x:row>
     <x:row r="2" spans="1:8"/>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="5" t="s">
+      <x:c r="A3" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="8" t="s"/>
-      <x:c r="F3" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
+      <x:c r="F3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H3" s="9" t="s">
@@ -784,23 +784,23 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="7" t="s">
+      <x:c r="F4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H4" s="9" t="s">
@@ -808,91 +808,91 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="s"/>
-      <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
+      <x:c r="A5" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s"/>
+      <x:c r="C5" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="s">
+      <x:c r="F5" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="s">
+      <x:c r="G5" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H5" s="9" t="s"/>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="s">
+      <x:c r="A8" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="F8" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G8" s="2" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H8" s="8" t="s"/>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="s">
+      <x:c r="A9" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G9" s="2" t="s"/>
+      <x:c r="G9" s="3" t="s"/>
       <x:c r="H9" s="8" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="s">
+      <x:c r="A10" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D10" s="4" t="s"/>
-      <x:c r="E10" s="6" t="s">
+      <x:c r="D10" s="5" t="s"/>
+      <x:c r="E10" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="9" t="s"/>
-      <x:c r="G10" s="2" t="s">
+      <x:c r="G10" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H10" s="8" t="s">
@@ -963,11 +963,11 @@
       <x:c r="F4" s="0" t="s"/>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="s"/>
-      <x:c r="C5" s="2" t="s">
+      <x:c r="A5" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s"/>
+      <x:c r="C5" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="8" t="s"/>
@@ -979,60 +979,60 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="4" t="s"/>
-      <x:c r="F6" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G6" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="7" t="s">
+      <x:c r="A6" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s"/>
+      <x:c r="F6" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H7" s="6" t="s">
+      <x:c r="A7" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G7" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="A8" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H8" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1044,49 +1044,49 @@
       <x:c r="C9" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F9" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G9" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H9" s="5" t="s">
+      <x:c r="F9" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="s">
+      <x:c r="A10" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F10" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G10" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H10" s="4" t="s"/>
+      <x:c r="F10" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="s"/>
     </x:row>
     <x:row r="11" spans="1:8">
-      <x:c r="A11" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F11" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G11" s="2" t="s"/>
-      <x:c r="H11" s="2" t="s">
+      <x:c r="A11" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="s"/>
+      <x:c r="H11" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1136,11 +1136,11 @@
       <x:c r="F2" s="0" t="s"/>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s"/>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s"/>
+      <x:c r="C3" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="9" t="s">
@@ -1152,49 +1152,49 @@
       <x:c r="H3" s="9" t="s"/>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s"/>
-      <x:c r="F4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="s"/>
+      <x:c r="A4" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s"/>
+      <x:c r="F4" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="s"/>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G5" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H5" s="7" t="s">
+      <x:c r="A5" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
+      <x:c r="A6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="F6" s="8" t="s"/>
@@ -1213,53 +1213,53 @@
       <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H7" s="5" t="s">
+      <x:c r="F7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="A8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="F8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H8" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F9" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H9" s="6" t="s">
+      <x:c r="A9" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G9" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H9" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1271,11 +1271,11 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="9" t="s"/>
-      <x:c r="F10" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G10" s="2" t="s"/>
-      <x:c r="H10" s="2" t="s">
+      <x:c r="F10" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="s"/>
+      <x:c r="H10" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1309,7 +1309,7 @@
       <x:c r="D2" s="0" t="s"/>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D3" s="9" t="s">
@@ -1317,43 +1317,43 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
+      <x:c r="A4" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
-      <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="7" t="s">
+      <x:c r="A5" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
-      <x:c r="A6" s="5" t="s"/>
-      <x:c r="D6" s="3" t="s">
+      <x:c r="A6" s="4" t="s"/>
+      <x:c r="D6" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="8" t="s"/>
-      <x:c r="D7" s="4" t="s">
+      <x:c r="D7" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
-      <x:c r="A8" s="3" t="s">
+      <x:c r="A8" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="s">
+      <x:c r="D8" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
-      <x:c r="A9" s="7" t="s">
+      <x:c r="A9" s="6" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D9" s="8" t="s"/>
@@ -1362,7 +1362,7 @@
       <x:c r="A10" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D10" s="5" t="s"/>
+      <x:c r="D10" s="4" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1394,78 +1394,78 @@
       <x:c r="F2" s="0" t="s"/>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s"/>
-      <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
+      <x:c r="A3" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s"/>
+      <x:c r="C3" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s"/>
-      <x:c r="F4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H4" s="5" t="s">
+      <x:c r="A4" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s"/>
+      <x:c r="F4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H4" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="s">
+      <x:c r="A5" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F5" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H5" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F6" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="4" t="s"/>
+      <x:c r="A6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F6" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G6" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="s"/>
     </x:row>
     <x:row r="7" spans="1:8">
       <x:c r="A7" s="8" t="s"/>
@@ -1475,24 +1475,24 @@
       <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H7" s="6" t="s">
+      <x:c r="F7" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G7" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="A8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F8" s="9" t="s">
@@ -1504,20 +1504,20 @@
       <x:c r="H8" s="9" t="s"/>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F9" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G9" s="2" t="s"/>
-      <x:c r="H9" s="2" t="s">
+      <x:c r="A9" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" s="3" t="s"/>
+      <x:c r="H9" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -109,14 +109,20 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+        <x:bgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1E90FF"/>
         <x:bgColor rgb="FF1E90FF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-        <x:bgColor rgb="FF90EE90"/>
+        <x:fgColor rgb="FF00CED1"/>
+        <x:bgColor rgb="FF00CED1"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -127,20 +133,14 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF00CED1"/>
-        <x:bgColor rgb="FF00CED1"/>
+        <x:fgColor rgb="FFDEB887"/>
+        <x:bgColor rgb="FFDEB887"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFCD5C5C"/>
         <x:bgColor rgb="FFCD5C5C"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFDEB887"/>
-        <x:bgColor rgb="FFDEB887"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -179,31 +179,31 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -212,10 +212,6 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -245,6 +241,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -562,7 +562,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -591,11 +591,11 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="A4" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s"/>
+      <x:c r="C4" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F4" s="2" t="s">
@@ -609,13 +609,13 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s"/>
+      <x:c r="A5" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s"/>
       <x:c r="F5" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -627,13 +627,13 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
+      <x:c r="A6" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="6" t="s">
@@ -656,29 +656,29 @@
       <x:c r="C7" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H7" s="8" t="s">
+      <x:c r="F7" s="7" t="s"/>
+      <x:c r="G7" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="8" t="s"/>
-      <x:c r="B8" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F8" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H8" s="5" t="s"/>
+      <x:c r="A8" s="7" t="s"/>
+      <x:c r="B8" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H8" s="3" t="s"/>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="2" t="s">
@@ -690,13 +690,13 @@
       <x:c r="C9" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F9" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G9" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H9" s="9" t="s"/>
+      <x:c r="F9" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H9" s="8" t="s"/>
     </x:row>
     <x:row r="10" spans="1:8">
       <x:c r="A10" s="6" t="s">
@@ -708,29 +708,29 @@
       <x:c r="C10" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F10" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G10" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H10" s="7" t="s">
+      <x:c r="F10" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:8">
-      <x:c r="A11" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B11" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="9" t="s"/>
-      <x:c r="F11" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G11" s="3" t="s"/>
-      <x:c r="H11" s="3" t="s">
+      <x:c r="A11" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="s"/>
+      <x:c r="F11" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s"/>
+      <x:c r="H11" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -754,47 +754,47 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8"/>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
+      <x:c r="A3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="s"/>
+      <x:c r="E3" s="7" t="s"/>
       <x:c r="F3" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H3" s="9" t="s">
+      <x:c r="H3" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="s">
+      <x:c r="A4" s="1" t="s"/>
+      <x:c r="B4" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="s">
+      <x:c r="E4" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="F4" s="2" t="s">
@@ -803,22 +803,22 @@
       <x:c r="G4" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H4" s="9" t="s">
+      <x:c r="H4" s="8" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s"/>
-      <x:c r="C5" s="7" t="s">
+      <x:c r="A5" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s"/>
+      <x:c r="C5" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="s">
+      <x:c r="E5" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="2" t="s">
@@ -827,7 +827,7 @@
       <x:c r="G5" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H5" s="9" t="s"/>
+      <x:c r="H5" s="8" t="s"/>
     </x:row>
     <x:row r="8" spans="1:8">
       <x:c r="A8" s="6" t="s">
@@ -839,19 +839,19 @@
       <x:c r="C8" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D8" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E8" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H8" s="8" t="s"/>
+      <x:c r="D8" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H8" s="7" t="s"/>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="6" t="s">
@@ -863,17 +863,17 @@
       <x:c r="C9" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E9" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F9" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G9" s="3" t="s"/>
-      <x:c r="H9" s="8" t="s">
+      <x:c r="D9" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s"/>
+      <x:c r="H9" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -887,15 +887,15 @@
       <x:c r="C10" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D10" s="5" t="s"/>
-      <x:c r="E10" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F10" s="9" t="s"/>
-      <x:c r="G10" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H10" s="8" t="s">
+      <x:c r="D10" s="3" t="s"/>
+      <x:c r="E10" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F10" s="8" t="s"/>
+      <x:c r="G10" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -940,19 +940,19 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
-      <x:c r="A2" s="1" t="s">
+      <x:c r="A2" s="9" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s"/>
       <x:c r="F2" s="0" t="s"/>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="1" t="s">
+      <x:c r="A3" s="9" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s"/>
@@ -963,29 +963,29 @@
       <x:c r="F4" s="0" t="s"/>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s"/>
-      <x:c r="C5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="s"/>
-      <x:c r="G5" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H5" s="8" t="s">
+      <x:c r="A5" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s"/>
+      <x:c r="C5" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="s"/>
+      <x:c r="G5" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H5" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s"/>
+      <x:c r="A6" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s"/>
       <x:c r="F6" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -997,22 +997,22 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F7" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G7" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H7" s="7" t="s">
+      <x:c r="A7" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1037,11 +1037,11 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="8" t="s"/>
-      <x:c r="B9" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="s">
+      <x:c r="A9" s="7" t="s"/>
+      <x:c r="B9" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
@@ -1064,13 +1064,13 @@
       <x:c r="C10" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F10" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H10" s="5" t="s"/>
+      <x:c r="F10" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="s"/>
     </x:row>
     <x:row r="11" spans="1:8">
       <x:c r="A11" s="6" t="s">
@@ -1082,29 +1082,29 @@
       <x:c r="C11" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G11" s="3" t="s"/>
-      <x:c r="H11" s="3" t="s">
+      <x:c r="F11" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s"/>
+      <x:c r="H11" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:8">
-      <x:c r="A12" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="s"/>
-      <x:c r="F12" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G12" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H12" s="9" t="s"/>
+      <x:c r="A12" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="s"/>
+      <x:c r="F12" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H12" s="8" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1127,7 +1127,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -1136,45 +1136,45 @@
       <x:c r="F2" s="0" t="s"/>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s"/>
-      <x:c r="C3" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G3" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H3" s="9" t="s"/>
+      <x:c r="A3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s"/>
+      <x:c r="C3" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H3" s="8" t="s"/>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s"/>
-      <x:c r="F4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H4" s="5" t="s"/>
+      <x:c r="A4" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
+      <x:c r="A5" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="6" t="s">
@@ -1197,20 +1197,20 @@
       <x:c r="C6" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="s"/>
-      <x:c r="G6" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="8" t="s">
+      <x:c r="F6" s="7" t="s"/>
+      <x:c r="G6" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="8" t="s"/>
-      <x:c r="B7" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="s">
+      <x:c r="A7" s="7" t="s"/>
+      <x:c r="B7" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
@@ -1253,29 +1253,29 @@
       <x:c r="C9" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F9" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G9" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H9" s="7" t="s">
+      <x:c r="F9" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G9" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="s"/>
-      <x:c r="F10" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G10" s="3" t="s"/>
-      <x:c r="H10" s="3" t="s">
+      <x:c r="A10" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="s"/>
+      <x:c r="F10" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s"/>
+      <x:c r="H10" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1300,7 +1300,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
@@ -1309,23 +1309,23 @@
       <x:c r="D2" s="0" t="s"/>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="9" t="s">
+      <x:c r="A3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
-      <x:c r="A4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="s">
+      <x:c r="A4" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
-      <x:c r="A5" s="7" t="s">
+      <x:c r="A5" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
@@ -1339,8 +1339,8 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
-      <x:c r="A7" s="8" t="s"/>
-      <x:c r="D7" s="5" t="s">
+      <x:c r="A7" s="7" t="s"/>
+      <x:c r="D7" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1348,7 +1348,7 @@
       <x:c r="A8" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="7" t="s">
+      <x:c r="D8" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1356,10 +1356,10 @@
       <x:c r="A9" s="6" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="s"/>
+      <x:c r="D9" s="7" t="s"/>
     </x:row>
     <x:row r="10" spans="1:4">
-      <x:c r="A10" s="9" t="s">
+      <x:c r="A10" s="8" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s"/>
@@ -1385,7 +1385,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -1394,11 +1394,11 @@
       <x:c r="F2" s="0" t="s"/>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s"/>
-      <x:c r="C3" s="3" t="s">
+      <x:c r="A3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s"/>
+      <x:c r="C3" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
@@ -1412,13 +1412,13 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s"/>
+      <x:c r="A4" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s"/>
       <x:c r="F4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1430,13 +1430,13 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
+      <x:c r="A5" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="2" t="s">
@@ -1459,29 +1459,29 @@
       <x:c r="C6" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="5" t="s"/>
+      <x:c r="F6" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G6" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="s"/>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="8" t="s"/>
-      <x:c r="B7" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F7" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G7" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H7" s="7" t="s">
+      <x:c r="A7" s="7" t="s"/>
+      <x:c r="B7" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1495,13 +1495,13 @@
       <x:c r="C8" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s"/>
+      <x:c r="F8" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="s"/>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="6" t="s">
@@ -1513,27 +1513,27 @@
       <x:c r="C9" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G9" s="3" t="s"/>
-      <x:c r="H9" s="3" t="s">
+      <x:c r="F9" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s"/>
+      <x:c r="H9" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="s"/>
-      <x:c r="F10" s="8" t="s"/>
-      <x:c r="G10" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H10" s="8" t="s">
+      <x:c r="A10" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="s"/>
+      <x:c r="F10" s="7" t="s"/>
+      <x:c r="G10" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -176,75 +176,75 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="10">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="10">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -566,10 +566,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:8">
-      <x:c r="C2" s="0" t="s"/>
-      <x:c r="F2" s="0" t="s"/>
-    </x:row>
+    <x:row r="2" spans="1:8"/>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="0" t="s">
         <x:v>1</x:v>
@@ -899,26 +896,11 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:8">
-      <x:c r="A11" s="0" t="s"/>
-      <x:c r="D11" s="0" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:8">
-      <x:c r="A12" s="0" t="s"/>
-      <x:c r="D12" s="0" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:8">
-      <x:c r="A13" s="0" t="s"/>
-      <x:c r="D13" s="0" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:8">
-      <x:c r="A14" s="0" t="s"/>
-      <x:c r="D14" s="0" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:8">
-      <x:c r="A15" s="0" t="s"/>
-      <x:c r="D15" s="0" t="s"/>
-    </x:row>
+    <x:row r="11" spans="1:8"/>
+    <x:row r="12" spans="1:8"/>
+    <x:row r="13" spans="1:8"/>
+    <x:row r="14" spans="1:8"/>
+    <x:row r="15" spans="1:8"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -948,20 +930,13 @@
       <x:c r="A2" s="9" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s"/>
-      <x:c r="F2" s="0" t="s"/>
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="9" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s"/>
-      <x:c r="F3" s="0" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:8">
-      <x:c r="C4" s="0" t="s"/>
-      <x:c r="F4" s="0" t="s"/>
-    </x:row>
+    </x:row>
+    <x:row r="4" spans="1:8"/>
     <x:row r="5" spans="1:8">
       <x:c r="A5" s="1" t="s">
         <x:v>4</x:v>
@@ -1131,10 +1106,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:8">
-      <x:c r="C2" s="0" t="s"/>
-      <x:c r="F2" s="0" t="s"/>
-    </x:row>
+    <x:row r="2" spans="1:8"/>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="1" t="s">
         <x:v>4</x:v>
@@ -1304,10 +1276,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0" t="s"/>
-      <x:c r="D2" s="0" t="s"/>
-    </x:row>
+    <x:row r="2" spans="1:4"/>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
         <x:v>4</x:v>
@@ -1389,10 +1358,7 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:8">
-      <x:c r="C2" s="0" t="s"/>
-      <x:c r="F2" s="0" t="s"/>
-    </x:row>
+    <x:row r="2" spans="1:8"/>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="1" t="s">
         <x:v>4</x:v>
